--- a/stories/arbres/ATOM-FAM.SEC.002-07.xlsx
+++ b/stories/arbres/ATOM-FAM.SEC.002-07.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Camille joue au jardin avec maman. Elle est près des pots. Un volet claque fort. Camille sent son ventre. C'est serré. Camille a peur. Camille marche vers maman. Elle prend sa main. Camille dit : maman, le volet a claqué. Mon ventre est serré. J'ai peur. Maman l'écoute. Maman dit : merci de raconter. Tu as le droit de le dire. Ce qui fait peur se raconte. On va raconter à papa ou maman. Parce qu'elle a raconté, Camille se sent moins seule. Maman reste tout près. Plus tard, à la maison, Camille le dit aussi à papa. Papa écoute. Camille se sent plus légère.</t>
+          <t>Camille joue au jardin avec maman. Elle est près des pots. Un volet claque fort. Camille sent son ventre. C'est serré. Camille a peur. Camille marche vers maman. Elle prend sa main. Maman, le volet a claqué. Mon ventre est serré. J'ai peur. Maman l'écoute. Merci de raconter. Tu as le droit de le dire. Ce qui fait peur se raconte. On va raconter à papa ou maman. Parce qu'elle a raconté, Camille se sent moins seule. Maman reste tout près. Plus tard, à la maison, Camille le dit aussi à papa. Papa écoute. Camille se sent plus légère.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,14 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Camille joue au jardin avec maman. Elle est près des pots. Un volet claque fort. Camille sent son ventre. C'est serré. Camille a peur. Camille marche vers maman. Elle prend sa main.
+enfant-f|Maman, le volet a claqué. Mon ventre est serré. J'ai peur. Maman l'écoute.
+maman|Merci de raconter. Tu as le droit de le dire. Ce qui fait peur se raconte. On va raconter à papa ou maman. Parce qu'elle a raconté, Camille se sent moins seule. Maman reste tout près. Plus tard, à la maison, Camille le dit aussi à papa. Papa écoute.
+narrateur|Camille se sent plus légère.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1469,6 +1493,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Camille a peur. Que fait-elle ?</t>
         </is>
       </c>
     </row>
@@ -1637,6 +1666,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Camille a senti la peur. Elle a marché vers maman. Elle a raconté. Papa et maman écoutent. Ce qui fait peur se raconte.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1799,6 +1833,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Camille s'assoit près de papa. Maman est là aussi. Sa main est chaude.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1961,6 +2000,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1979,7 +2023,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1996,6 +2040,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-FAM.SEC.002-07.xlsx
+++ b/stories/arbres/ATOM-FAM.SEC.002-07.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1313,6 +1318,11 @@
 narrateur|Camille se sent plus légère.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1500,6 +1510,7 @@
           <t>narrateur|Camille a peur. Que fait-elle ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1671,6 +1682,7 @@
           <t>narrateur|Camille a senti la peur. Elle a marché vers maman. Elle a raconté. Papa et maman écoutent. Ce qui fait peur se raconte.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1838,6 +1850,7 @@
           <t>narrateur|Camille s'assoit près de papa. Maman est là aussi. Sa main est chaude.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2005,6 +2018,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2023,7 +2037,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2047,6 +2061,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2061,7 +2089,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2248,6 +2276,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-FAM.SEC.002-07.xlsx
+++ b/stories/arbres/ATOM-FAM.SEC.002-07.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Camille raconte ce qui fait peur</t>
+          <t>Nino raconte le volet</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Un arrosoir laisse une goutte. Un volet claque. Nino raconte à maman, puis à papa.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Camille joue au jardin avec maman. Elle est près des pots. Un volet claque fort. Camille sent son ventre. C'est serré. Camille a peur. Camille marche vers maman. Elle prend sa main. Maman, le volet a claqué. Mon ventre est serré. J'ai peur. Maman l'écoute. Merci de raconter. Tu as le droit de le dire. Ce qui fait peur se raconte. On va raconter à papa ou maman. Parce qu'elle a raconté, Camille se sent moins seule. Maman reste tout près. Plus tard, à la maison, Camille le dit aussi à papa. Papa écoute. Camille se sent plus légère.</t>
+          <t>Un arrosoir laisse une goutte. La goutte tombe dans la terre. Elle fait un petit rond. Les pots d'argile sont tièdes. Une feuille de tomate sent fort. Elle est un peu rêche. Le gravier du jardin craque. Nino, l'arrosoir a encore de l'eau. En ce moment, Nino est près des pots. Il touche une feuille de tomate. Elle sent fort, maman. Oui. C'est la tomate. Un volet claque fort. Le bois tape contre le mur. Nino sent son ventre. Le ventre est serré. Nino a peur. Il pose l'arrosoir. Il marche vers maman. Il prend sa main. Maman, le volet a claqué. Mon ventre est serré. J'ai peur. Merci de raconter. Tu as le droit de le dire. Ce qui fait peur se raconte. On va raconter à papa ou maman. Je reste tout près. Le volet est calme ? Oui, Nino. Bravo. Tu as fait du bon travail. Maman tient sa main. La main de maman est chaude. Le volet ne bouge plus. Parce que tu as raconté. Tu es moins seul. Oui. Plus tard, ils rentrent à la maison. Les chaussures laissent un peu de terre. Papa range un linge. Vous rentrez du jardin ? Nino a quelque chose à dire. Nino marche vers papa. Papa, le volet a claqué. Mon ventre était serré. J'ai raconté à maman. Merci de raconter. Tu as le droit de le dire. Ce qui fait peur se raconte. On va raconter à papa ou maman. Je me sens plus léger. Bravo, Nino. Tu as fait du bon travail. Nino s'assoit près de papa. Maman pose l'arrosoir près de la porte. Une goutte tombe encore.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,10 +1324,64 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Camille joue au jardin avec maman. Elle est près des pots. Un volet claque fort. Camille sent son ventre. C'est serré. Camille a peur. Camille marche vers maman. Elle prend sa main.
-enfant-f|Maman, le volet a claqué. Mon ventre est serré. J'ai peur. Maman l'écoute.
-maman|Merci de raconter. Tu as le droit de le dire. Ce qui fait peur se raconte. On va raconter à papa ou maman. Parce qu'elle a raconté, Camille se sent moins seule. Maman reste tout près. Plus tard, à la maison, Camille le dit aussi à papa. Papa écoute.
-narrateur|Camille se sent plus légère.</t>
+          <t>narrateur|Un arrosoir laisse une goutte.
+narrateur|La goutte tombe dans la terre.
+narrateur|Elle fait un petit rond.
+narrateur|Les pots d'argile sont tièdes.
+narrateur|Une feuille de tomate sent fort.
+narrateur|Elle est un peu rêche.
+narrateur|Le gravier du jardin craque.
+maman|Nino, l'arrosoir a encore de l'eau.
+narrateur|En ce moment, Nino est près des pots.
+narrateur|Il touche une feuille de tomate.
+enfant-m|Elle sent fort, maman.
+maman|Oui.
+maman|C'est la tomate.
+narrateur|Un volet claque fort.
+narrateur|Le bois tape contre le mur.
+narrateur|Nino sent son ventre.
+narrateur|Le ventre est serré.
+narrateur|Nino a peur.
+narrateur|Il pose l'arrosoir.
+narrateur|Il marche vers maman.
+narrateur|Il prend sa main.
+enfant-m|Maman, le volet a claqué.
+enfant-m|Mon ventre est serré.
+enfant-m|J'ai peur.
+maman|Merci de raconter.
+maman|Tu as le droit de le dire.
+maman|Ce qui fait peur se raconte.
+maman|On va raconter à papa ou maman.
+maman|Je reste tout près.
+enfant-m|Le volet est calme ?
+maman|Oui, Nino.
+maman|Bravo.
+maman|Tu as fait du bon travail.
+narrateur|Maman tient sa main.
+narrateur|La main de maman est chaude.
+narrateur|Le volet ne bouge plus.
+maman|Parce que tu as raconté.
+maman|Tu es moins seul.
+enfant-m|Oui.
+narrateur|Plus tard, ils rentrent à la maison.
+narrateur|Les chaussures laissent un peu de terre.
+narrateur|Papa range un linge.
+papa|Vous rentrez du jardin ?
+maman|Nino a quelque chose à dire.
+narrateur|Nino marche vers papa.
+enfant-m|Papa, le volet a claqué.
+enfant-m|Mon ventre était serré.
+enfant-m|J'ai raconté à maman.
+papa|Merci de raconter.
+papa|Tu as le droit de le dire.
+papa|Ce qui fait peur se raconte.
+papa|On va raconter à papa ou maman.
+enfant-m|Je me sens plus léger.
+papa|Bravo, Nino.
+papa|Tu as fait du bon travail.
+narrateur|Nino s'assoit près de papa.
+narrateur|Maman pose l'arrosoir près de la porte.
+narrateur|Une goutte tombe encore.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -1347,7 +1413,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Camille a peur. Que fait-elle ?</t>
+          <t>Nino a peur. Que fait-il ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1507,7 +1573,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Camille a peur. Que fait-elle ?</t>
+          <t>narrateur|Nino a peur.
+narrateur|Que fait-il ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1535,7 +1602,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Camille a senti la peur. Elle a marché vers maman. Elle a raconté. Papa et maman écoutent. Ce qui fait peur se raconte.</t>
+          <t>Nino a senti la peur. Il a marché vers maman. Il a raconté. Tu as raconté le volet ? Oui. Puis à papa aussi. Bravo. Ce qui fait peur se raconte. On va raconter à papa ou maman. L'arrosoir reste près de la porte. La feuille de tomate sent encore.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1679,7 +1746,17 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Camille a senti la peur. Elle a marché vers maman. Elle a raconté. Papa et maman écoutent. Ce qui fait peur se raconte.</t>
+          <t>narrateur|Nino a senti la peur.
+narrateur|Il a marché vers maman.
+narrateur|Il a raconté.
+maman|Tu as raconté le volet ?
+enfant-m|Oui.
+papa|Puis à papa aussi.
+papa|Bravo.
+maman|Ce qui fait peur se raconte.
+maman|On va raconter à papa ou maman.
+narrateur|L'arrosoir reste près de la porte.
+narrateur|La feuille de tomate sent encore.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1707,7 +1784,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Camille s'assoit près de papa. Maman est là aussi. Sa main est chaude.</t>
+          <t>Nino s'assoit près de papa. Maman s'assoit aussi. Tu es là, avec nous. Le volet est calme maintenant. Oui. J'ai raconté. Bravo. C'est du bon travail. Un peu de terre sèche au paillasson. La goutte de l'arrosoir a fini. On reste encore un peu. D'accord.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1847,7 +1924,18 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Camille s'assoit près de papa. Maman est là aussi. Sa main est chaude.</t>
+          <t>narrateur|Nino s'assoit près de papa.
+narrateur|Maman s'assoit aussi.
+papa|Tu es là, avec nous.
+maman|Le volet est calme maintenant.
+enfant-m|Oui.
+enfant-m|J'ai raconté.
+papa|Bravo.
+papa|C'est du bon travail.
+narrateur|Un peu de terre sèche au paillasson.
+narrateur|La goutte de l'arrosoir a fini.
+maman|On reste encore un peu.
+enfant-m|D'accord.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1875,7 +1963,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>L'arrosoir dort près de la porte. J'ai raconté. Bravo, Nino. On t'écoute. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2015,7 +2103,11 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|L'arrosoir dort près de la porte.
+enfant-m|J'ai raconté.
+maman|Bravo, Nino.
+papa|On t'écoute.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2037,7 +2129,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2075,6 +2167,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-FAM.SEC.002-07.xlsx
+++ b/stories/arbres/ATOM-FAM.SEC.002-07.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Un arrosoir laisse une goutte. La goutte tombe dans la terre. Elle fait un petit rond. Les pots d'argile sont tièdes. Une feuille de tomate sent fort. Elle est un peu rêche. Le gravier du jardin craque. Nino, l'arrosoir a encore de l'eau. En ce moment, Nino est près des pots. Il touche une feuille de tomate. Elle sent fort, maman. Oui. C'est la tomate. Un volet claque fort. Le bois tape contre le mur. Nino sent son ventre. Le ventre est serré. Nino a peur. Il pose l'arrosoir. Il marche vers maman. Il prend sa main. Maman, le volet a claqué. Mon ventre est serré. J'ai peur. Merci de raconter. Tu as le droit de le dire. Ce qui fait peur se raconte. On va raconter à papa ou maman. Je reste tout près. Le volet est calme ? Oui, Nino. Bravo. Tu as fait du bon travail. Maman tient sa main. La main de maman est chaude. Le volet ne bouge plus. Parce que tu as raconté. Tu es moins seul. Oui. Plus tard, ils rentrent à la maison. Les chaussures laissent un peu de terre. Papa range un linge. Vous rentrez du jardin ? Nino a quelque chose à dire. Nino marche vers papa. Papa, le volet a claqué. Mon ventre était serré. J'ai raconté à maman. Merci de raconter. Tu as le droit de le dire. Ce qui fait peur se raconte. On va raconter à papa ou maman. Je me sens plus léger. Bravo, Nino. Tu as fait du bon travail. Nino s'assoit près de papa. Maman pose l'arrosoir près de la porte. Une goutte tombe encore.</t>
+          <t>Un arrosoir laisse une goutte. La goutte tombe dans la terre. Elle fait un petit rond. Les pots d'argile sont tièdes. Une feuille de tomate sent fort. Elle est un peu rêche. Le gravier du jardin craque. Nino, l'arrosoir a encore de l'eau. En ce moment, Nino est près des pots. Il touche une feuille de tomate. Elle sent fort, maman. Oui. C'est la tomate. Un volet claque fort. Le bois tape contre le mur. Nino sent son ventre. Le ventre est serré. Nino a peur. Il pose l'arrosoir. Il marche vers maman. Il prend sa main. Maman, le volet a claqué. Mon ventre est serré. J'ai peur. Merci de raconter. Tu as le droit de le dire. Ce qui fait peur se raconte. On va raconter à papa ou maman. Je reste tout près. Le volet est calme ? Oui, Nino. Bravo. Maman tient sa main. La main de maman est chaude. Le volet ne bouge plus. Parce que tu as raconté. Tu es moins seul. Oui. Plus tard, ils rentrent à la maison. Les chaussures laissent un peu de terre. Papa range un linge. Vous rentrez du jardin ? Nino a quelque chose à dire. Nino marche vers papa. Papa, le volet a claqué. Mon ventre était serré. J'ai raconté à maman. Merci de raconter. Tu as le droit de le dire. Ce qui fait peur se raconte. On va raconter à papa ou maman. Je me sens plus léger. Bravo, Nino. Nino s'assoit près de papa. Maman pose l'arrosoir près de la porte. Une goutte tombe encore.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Camille joue au jardin avec maman. Elle est près des pots. Un volet claque fort. Camille sent son ventre. C'est serré. Camille a &lt;emphasis level="moderate"&gt;peur&lt;/emphasis&gt;. Camille marche vers maman. Elle prend sa main. Camille dit : maman, le volet a claqué. Mon ventre est serré. J'ai peur. Maman l'écoute. Maman dit : merci de raconter. Tu as le droit de le dire. Ce qui fait peur se raconte. On va raconter à papa ou maman. Parce qu'elle a raconté, Camille se sent moins seule. Maman reste tout près. Plus tard, à la maison, Camille le dit aussi à papa. Papa écoute. Camille se sent plus légère.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Un arrosoir laisse une goutte. La goutte tombe dans la terre. Elle fait un petit rond. Les pots d'argile sont tièdes. Une feuille de tomate sent fort. Elle est un peu rêche. Le gravier du jardin craque. Nino, l'arrosoir a encore de l'eau. En ce moment, Nino est près des pots. Il touche une feuille de tomate. Elle sent fort, maman. Oui. C'est la tomate. Un volet claque fort. Le bois tape contre le mur. Nino sent son ventre. Le ventre est serré. Nino a peur. Il pose l'arrosoir. Il marche vers maman. Il prend sa main. Maman, le volet a claqué. Mon ventre est serré. J'ai peur. Merci de raconter. Tu as le droit de le dire. Ce qui fait peur se raconte. On va raconter à papa ou maman. Je reste tout près. Le volet est calme ? Oui, Nino. Bravo. Maman tient sa main. La main de maman est chaude. Le volet ne bouge plus. Parce que tu as raconté. Tu es moins seul. Oui. Plus tard, ils rentrent à la maison. Les chaussures laissent un peu de terre. Papa range un linge. Vous rentrez du jardin ? Nino a quelque chose à dire. Nino marche vers papa. Papa, le volet a claqué. Mon ventre était serré. J'ai raconté à maman. Merci de raconter. Tu as le droit de le dire. Ce qui fait peur se raconte. On va raconter à papa ou maman. Je me sens plus léger. Bravo, Nino. Nino s'assoit près de papa. Maman pose l'arrosoir près de la porte. Une goutte tombe encore.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1356,7 +1356,6 @@
 enfant-m|Le volet est calme ?
 maman|Oui, Nino.
 maman|Bravo.
-maman|Tu as fait du bon travail.
 narrateur|Maman tient sa main.
 narrateur|La main de maman est chaude.
 narrateur|Le volet ne bouge plus.
@@ -1378,7 +1377,6 @@
 papa|On va raconter à papa ou maman.
 enfant-m|Je me sens plus léger.
 papa|Bravo, Nino.
-papa|Tu as fait du bon travail.
 narrateur|Nino s'assoit près de papa.
 narrateur|Maman pose l'arrosoir près de la porte.
 narrateur|Une goutte tombe encore.</t>
@@ -1418,7 +1416,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Camille a &lt;emphasis level="moderate"&gt;peur&lt;/emphasis&gt;. Que fait-elle ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nino a peur. Que fait-il ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1577,7 +1575,6 @@
 narrateur|Que fait-il ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1607,7 +1604,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Camille a senti la &lt;emphasis level="moderate"&gt;peur&lt;/emphasis&gt;. Elle a marché vers maman. Elle a raconté. Papa et maman écoutent. Ce qui fait peur se raconte.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nino a senti la peur. Il a marché vers maman. Il a raconté. Tu as raconté le volet ? Oui. Puis à papa aussi. Bravo. Ce qui fait peur se raconte. On va raconter à papa ou maman. L'arrosoir reste près de la porte. La feuille de tomate sent encore.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1759,7 +1756,6 @@
 narrateur|La feuille de tomate sent encore.</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1784,12 +1780,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Nino s'assoit près de papa. Maman s'assoit aussi. Tu es là, avec nous. Le volet est calme maintenant. Oui. J'ai raconté. Bravo. C'est du bon travail. Un peu de terre sèche au paillasson. La goutte de l'arrosoir a fini. On reste encore un peu. D'accord.</t>
+          <t>Nino s'assoit près de papa. Maman s'assoit aussi. Tu es là, avec nous. Le volet est calme maintenant. Oui. J'ai raconté. Bravo. Un peu de terre sèche au paillasson. La goutte de l'arrosoir a fini. On reste encore un peu. D'accord.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Camille s'assoit près de papa. Maman est là aussi. Sa &lt;emphasis level="moderate"&gt;main&lt;/emphasis&gt; est chaude.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nino s'assoit près de papa. Maman s'assoit aussi. Tu es là, avec nous. Le volet est calme maintenant. Oui. J'ai raconté. Bravo. Un peu de terre sèche au paillasson. La goutte de l'arrosoir a fini. On reste encore un peu. D'accord.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1931,14 +1927,12 @@
 enfant-m|Oui.
 enfant-m|J'ai raconté.
 papa|Bravo.
-papa|C'est du bon travail.
 narrateur|Un peu de terre sèche au paillasson.
 narrateur|La goutte de l'arrosoir a fini.
 maman|On reste encore un peu.
 enfant-m|D'accord.</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1963,12 +1957,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'arrosoir dort près de la porte. J'ai raconté. Bravo, Nino. On t'écoute. L'histoire est finie.</t>
+          <t>L'arrosoir dort près de la porte. J'ai raconté. Bravo, Nino. On t'écoute.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>L'arrosoir dort près de la porte. J'ai raconté. Bravo, Nino. On t'écoute.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2106,11 +2100,9 @@
           <t>narrateur|L'arrosoir dort près de la porte.
 enfant-m|J'ai raconté.
 maman|Bravo, Nino.
-papa|On t'écoute.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+papa|On t'écoute.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2129,7 +2121,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2174,6 +2166,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-FAM.SEC.002-07.xlsx
+++ b/stories/arbres/ATOM-FAM.SEC.002-07.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>jardin puis maison</t>
+          <t>jardin, pots, puis maison</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Camille, maman, papa</t>
+          <t>Nino, maman, papa</t>
         </is>
       </c>
     </row>
